--- a/artfynd/A 53142-2024 artfynd.xlsx
+++ b/artfynd/A 53142-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152200</v>
+        <v>121152201</v>
       </c>
       <c r="B2" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784295</v>
+        <v>784318</v>
       </c>
       <c r="R2" t="n">
-        <v>7345410</v>
+        <v>7345420</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152201</v>
+        <v>121152200</v>
       </c>
       <c r="B3" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784318</v>
+        <v>784295</v>
       </c>
       <c r="R3" t="n">
-        <v>7345420</v>
+        <v>7345410</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 53142-2024 artfynd.xlsx
+++ b/artfynd/A 53142-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152201</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152200</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53142-2024 artfynd.xlsx
+++ b/artfynd/A 53142-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152201</v>
       </c>
       <c r="B2" t="n">
-        <v>91271</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152200</v>
       </c>
       <c r="B3" t="n">
-        <v>91271</v>
+        <v>91272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53142-2024 artfynd.xlsx
+++ b/artfynd/A 53142-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152201</v>
+        <v>121152200</v>
       </c>
       <c r="B2" t="n">
-        <v>91272</v>
+        <v>91275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784318</v>
+        <v>784295</v>
       </c>
       <c r="R2" t="n">
-        <v>7345420</v>
+        <v>7345410</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152200</v>
+        <v>121152201</v>
       </c>
       <c r="B3" t="n">
-        <v>91272</v>
+        <v>91275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784295</v>
+        <v>784318</v>
       </c>
       <c r="R3" t="n">
-        <v>7345410</v>
+        <v>7345420</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
